--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NEVADA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NEVADA_2024.xlsx
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C150">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C291">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Santa Ana Tlapacoya</t>
+          <t>Santa Ana Tlapacoyan</t>
         </is>
       </c>
       <c r="C844">
